--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table35.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table35.xlsx
@@ -52,7 +52,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -193,23 +193,16 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -238,42 +231,42 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
+  <dxfs count="368">
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
@@ -281,77 +274,364 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -370,119 +650,49 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -493,12 +703,374 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FF00B050"/>
@@ -523,6 +1095,1713 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1584,7 +3863,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="ROW LABLE">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="ROW LABLE">
   <location ref="A3:B88" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" showAll="0">
@@ -1916,102 +4195,14 @@
   <dataFields count="1">
     <dataField name="Sum of Amount" fld="2" baseField="6" baseItem="4" numFmtId="3"/>
   </dataFields>
-  <formats count="38">
-    <format dxfId="37">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="2">
-            <x v="0"/>
-            <x v="4"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="36">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="2">
-            <x v="0"/>
-            <x v="4"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="35">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="2">
-            <x v="10"/>
-            <x v="14"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="34">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="2">
-            <x v="5"/>
-            <x v="9"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="33">
+  <formats count="85">
+    <format dxfId="367">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="366">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="365">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="5">
           <reference field="0" count="2">
@@ -2033,7 +4224,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="364">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="5">
           <reference field="0" count="3">
@@ -2056,16 +4247,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="363">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="5">
           <reference field="0" count="3">
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
+            <x v="16"/>
+            <x v="17"/>
+            <x v="18"/>
           </reference>
           <reference field="3" count="1" selected="0">
-            <x v="0"/>
+            <x v="1"/>
           </reference>
           <reference field="4" count="1" selected="0">
             <x v="0"/>
@@ -2074,35 +4265,12 @@
             <x v="1"/>
           </reference>
           <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="28">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="3">
-            <x v="11"/>
-            <x v="12"/>
-            <x v="13"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="27">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="362">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="5">
           <reference field="0" count="3">
@@ -2114,7 +4282,7 @@
             <x v="1"/>
           </reference>
           <reference field="4" count="1" selected="0">
-            <x v="0"/>
+            <x v="1"/>
           </reference>
           <reference field="5" count="1" selected="0">
             <x v="1"/>
@@ -2125,7 +4293,430 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="361">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="360">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="359">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="0"/>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="358">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="357">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="356">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="3" count="0"/>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="355">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="354">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="0"/>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="353">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="3" count="1">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="352">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="8">
+            <x v="0"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="14"/>
+            <x v="15"/>
+            <x v="19"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="351">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="12">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="11"/>
+            <x v="12"/>
+            <x v="13"/>
+            <x v="16"/>
+            <x v="17"/>
+            <x v="18"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="350">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="6">
+            <x v="5"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="14"/>
+            <x v="15"/>
+            <x v="19"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="349">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="6">
+            <x v="5"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="14"/>
+            <x v="15"/>
+            <x v="19"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="348">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="3" count="0"/>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="347">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="9">
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="11"/>
+            <x v="12"/>
+            <x v="13"/>
+            <x v="16"/>
+            <x v="17"/>
+            <x v="18"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="346">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="4">
+            <x v="0"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="345">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="11">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="14"/>
+            <x v="15"/>
+            <x v="19"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="344">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="3" count="1">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="343">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="3">
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="342">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="12">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="11"/>
+            <x v="12"/>
+            <x v="13"/>
+            <x v="16"/>
+            <x v="17"/>
+            <x v="18"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="341">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="340">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="13">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="11"/>
+            <x v="12"/>
+            <x v="13"/>
+            <x v="15"/>
+            <x v="19"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="339">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="5">
           <reference field="0" count="3">
@@ -2137,7 +4728,7 @@
             <x v="1"/>
           </reference>
           <reference field="4" count="1" selected="0">
-            <x v="0"/>
+            <x v="1"/>
           </reference>
           <reference field="5" count="1" selected="0">
             <x v="1"/>
@@ -2148,172 +4739,41 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="251">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="2">
+            <x v="2"/>
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="250">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="5">
-          <reference field="0" count="2">
-            <x v="0"/>
-            <x v="4"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="24">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="2">
-            <x v="0"/>
-            <x v="4"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="23">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="2">
-            <x v="10"/>
-            <x v="14"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="22">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="2">
-            <x v="5"/>
-            <x v="9"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="21">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="2">
-            <x v="15"/>
-            <x v="19"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="3">
+          <reference field="0" count="9">
             <x v="1"/>
             <x v="2"/>
             <x v="3"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="19">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="3">
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="18">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="0" count="3">
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
             <x v="11"/>
             <x v="12"/>
             <x v="13"/>
           </reference>
           <reference field="3" count="1" selected="0">
-            <x v="1"/>
+            <x v="0"/>
           </reference>
           <reference field="4" count="1" selected="0">
             <x v="1"/>
@@ -2322,18 +4782,42 @@
             <x v="1"/>
           </reference>
           <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="17">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="113">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="111">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="109">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="5">
-          <reference field="0" count="3">
+          <reference field="0" count="6">
             <x v="6"/>
             <x v="7"/>
             <x v="8"/>
+            <x v="11"/>
+            <x v="12"/>
+            <x v="13"/>
           </reference>
           <reference field="3" count="1" selected="0">
             <x v="1"/>
@@ -2345,15 +4829,190 @@
             <x v="1"/>
           </reference>
           <reference field="6" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="16">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="108">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="106">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="103">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="3" count="0"/>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="101">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="99">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="5">
-          <reference field="0" count="3">
+          <reference field="0" count="15">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="9"/>
+            <x v="10"/>
+            <x v="11"/>
+            <x v="12"/>
+            <x v="13"/>
+            <x v="14"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="52">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="3">
+          <reference field="3" count="0"/>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="45">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="12">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
+            <x v="11"/>
+            <x v="12"/>
+            <x v="13"/>
+            <x v="15"/>
+            <x v="16"/>
+            <x v="19"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="43">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="42">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="6">
+            <x v="6"/>
+            <x v="7"/>
+            <x v="8"/>
             <x v="16"/>
             <x v="17"/>
             <x v="18"/>
@@ -2362,36 +5021,30 @@
             <x v="1"/>
           </reference>
           <reference field="4" count="1" selected="0">
-            <x v="1"/>
+            <x v="0"/>
           </reference>
           <reference field="5" count="1" selected="0">
             <x v="1"/>
           </reference>
           <reference field="6" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="15">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="14">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="13">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="4" count="1" selected="0">
             <x v="0"/>
           </reference>
           <reference field="5" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="12">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="3">
           <reference field="3" count="1">
@@ -2401,16 +5054,84 @@
             <x v="0"/>
           </reference>
           <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="11">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="37">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="7">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="5"/>
+            <x v="9"/>
+            <x v="15"/>
+            <x v="19"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="34">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="33">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="3" count="1">
-            <x v="1"/>
+            <x v="0"/>
           </reference>
           <reference field="4" count="1" selected="0">
             <x v="0"/>
@@ -2421,38 +5142,128 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="2">
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="9">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+    <format dxfId="32">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="31">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="3" count="1">
-            <x v="0"/>
+            <x v="1"/>
           </reference>
           <reference field="4" count="1" selected="0">
             <x v="0"/>
           </reference>
           <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="8">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="29">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="27">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="26">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="3" count="1">
-            <x v="1"/>
+            <x v="0"/>
           </reference>
           <reference field="4" count="1" selected="0">
             <x v="0"/>
@@ -2463,38 +5274,137 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="2">
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="5" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+    <format dxfId="24">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="22">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="3" count="1">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
           </reference>
           <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="5">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="21">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="20">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="18">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="16">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="3" count="1">
-            <x v="1"/>
+            <x v="0"/>
           </reference>
           <reference field="4" count="1" selected="0">
             <x v="1"/>
@@ -2505,38 +5415,128 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="2">
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-          <reference field="5" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="3">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+    <format dxfId="15">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="14">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="3" count="1">
-            <x v="0"/>
+            <x v="1"/>
           </reference>
           <reference field="4" count="1" selected="0">
             <x v="1"/>
           </reference>
           <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="11">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="10">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="9">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="3" count="1">
-            <x v="1"/>
+            <x v="0"/>
           </reference>
           <reference field="4" count="1" selected="0">
             <x v="1"/>
@@ -2547,11 +5547,116 @@
         </references>
       </pivotArea>
     </format>
+    <format dxfId="7">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="3" count="1">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="4">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="2">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="4">
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="6" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
     <format dxfId="1">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -2859,682 +5964,682 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="9">
         <v>71565</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="9">
         <v>18915</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="9">
         <v>16500</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="9">
         <v>15000</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>10000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>5000</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="9">
         <v>1500</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>1000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="9">
         <v>2415</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="9">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="9">
         <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="9">
         <v>2250</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>1500</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>750</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="9">
         <v>52650</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="9">
         <v>49500</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="9">
         <v>45000</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>15000</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <v>20000</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="1">
         <v>10000</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="9">
         <v>4500</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="1">
         <v>1500</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="1">
         <v>2000</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="1">
         <v>1000</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="9">
         <v>3150</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="9">
         <v>450</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="1">
         <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="1">
         <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="9">
         <v>900</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="1">
         <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="1">
         <v>400</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="1">
         <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="9">
         <v>1800</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="1">
         <v>600</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="1">
         <v>800</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="1">
         <v>400</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="9">
         <v>107347.5</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="9">
         <v>28372.5</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="9">
         <v>24750</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="9">
         <v>22500</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="1">
         <v>15000</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="1">
         <v>7500</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="9">
         <v>2250</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="1">
         <v>1500</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="1">
         <v>750</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="9">
         <v>3622.5</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="9">
         <v>22.5</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="1">
         <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="1">
         <v>7.5</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="9">
         <v>225</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="1">
         <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="9">
         <v>3375</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="1">
         <v>2250</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="1">
         <v>1125</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="9">
         <v>78975</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="9">
         <v>74250</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="9">
         <v>67500</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="1">
         <v>22500</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="1">
         <v>30000</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="1">
         <v>15000</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="9">
         <v>6750</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="1">
         <v>2250</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B73" s="2">
+      <c r="B73" s="1">
         <v>3000</v>
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B74" s="2">
+      <c r="B74" s="1">
         <v>1500</v>
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="9">
         <v>4725</v>
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B76" s="2">
+      <c r="B76" s="9">
         <v>675</v>
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="1">
         <v>225</v>
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="1">
         <v>300</v>
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B79" s="2">
+      <c r="B79" s="1">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B80" s="2">
+      <c r="B80" s="9">
         <v>1350</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B81" s="2">
+      <c r="B81" s="1">
         <v>450</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B82" s="2">
+      <c r="B82" s="1">
         <v>600</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="1">
         <v>300</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="9">
         <v>2700</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B85" s="2">
+      <c r="B85" s="1">
         <v>900</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B86" s="2">
+      <c r="B86" s="1">
         <v>1200</v>
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B87" s="2">
+      <c r="B87" s="1">
         <v>600</v>
       </c>
     </row>
